--- a/rentabilidades/rentabilidade_07_2025_agrupada.xlsx
+++ b/rentabilidades/rentabilidade_07_2025_agrupada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\projetos\Robô para cálculo de comissões 2.0\rentabilidades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CC1049-05E1-4885-8562-FA3E3CBDACA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FD59B5-BADB-4CCF-94F0-4CC07C72717A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
